--- a/src/onlyMain/resources/节气数据.xlsx
+++ b/src/onlyMain/resources/节气数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Ecliptic\src\onlyMain\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\EclipticSeasons\src\onlyMain\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0B6EB0-1C42-412B-BF61-4C06EB398F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98126537-EF22-4B50-87CE-B7B3FB5C5C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{9B4BF41A-40D4-4F30-95C5-B63DB59132D5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="130">
   <si>
     <t>立春</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -436,6 +436,121 @@
   </si>
   <si>
     <t>降雨基础概率为0.01/tick。对于无雨群系为0，几乎无雨群系为1%，少雨群系为10%，适量雨群系为40%，多雨群系为100%。最后乘群系概率（最少设计概率一半，除非无雨）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>热带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节气等价表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微凉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微暖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>略热</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>极寒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏季</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏季平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏秋平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春夏平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不生长</t>
+  </si>
+  <si>
+    <t>不生长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>除夏季沿用立夏和小满平均外，其余早中晚沿用春夏秋的两个平均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冬+早春平均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生长概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础概率，依据标签和附加数据包确定</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +622,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -530,13 +645,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -573,6 +717,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -582,11 +732,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -907,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349BBA73-A7C7-466C-AA4F-FD3A9580A8DC}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="7.5" style="1" customWidth="1"/>
@@ -924,27 +1080,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>44</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
       <c r="J1" s="10" t="s">
         <v>49</v>
       </c>
@@ -957,20 +1113,20 @@
       <c r="M1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12" t="s">
+      <c r="O1" s="14"/>
+      <c r="P1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="12"/>
+      <c r="Q1" s="14"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="10" t="s">
         <v>56</v>
       </c>
@@ -998,13 +1154,13 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1039,9 +1195,9 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1076,9 +1232,9 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1113,9 +1269,9 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
       <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1148,9 +1304,9 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1187,9 +1343,9 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
       <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1224,13 +1380,13 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1267,9 +1423,9 @@
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
       <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
@@ -1308,9 +1464,9 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1351,9 +1507,9 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1392,9 +1548,9 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1441,9 +1597,9 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1488,13 +1644,13 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -1539,9 +1695,9 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
       <c r="D16" s="6" t="s">
         <v>13</v>
       </c>
@@ -1584,9 +1740,9 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15" t="s">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -1625,9 +1781,9 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="6" t="s">
         <v>15</v>
       </c>
@@ -1664,9 +1820,9 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15" t="s">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -1711,9 +1867,9 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
       <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
@@ -1756,13 +1912,13 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="16" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -1805,9 +1961,9 @@
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="8" t="s">
         <v>19</v>
       </c>
@@ -1848,9 +2004,9 @@
       <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -1885,9 +2041,9 @@
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
       <c r="D24" s="8" t="s">
         <v>21</v>
       </c>
@@ -1920,9 +2076,9 @@
       <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="8" t="s">
@@ -1957,9 +2113,9 @@
       <c r="Q25" s="8"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
       <c r="D26" s="8" t="s">
         <v>23</v>
       </c>
@@ -1992,127 +2148,127 @@
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
     </row>
     <row r="34" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G34" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I34" s="12"/>
+      <c r="I34" s="14"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="I35" s="12"/>
+      <c r="I35" s="14"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="10" t="s">
@@ -2228,13 +2384,548 @@
       <c r="G46" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="12"/>
+      <c r="I46" s="14"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G54" t="s">
+        <v>128</v>
+      </c>
+      <c r="H54" t="s">
+        <v>103</v>
+      </c>
+      <c r="I54" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G55" t="s">
+        <v>124</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="18"/>
+      <c r="F56" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I56" s="18"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="18"/>
+      <c r="F57" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G57" s="20"/>
+      <c r="H57" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="18"/>
+      <c r="F58" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G58" s="20"/>
+      <c r="H58" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I58" s="18"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="18"/>
+      <c r="F59" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G59" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I59" s="18"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="18"/>
+      <c r="F60" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G60" s="20"/>
+      <c r="H60" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I60" s="18"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="18"/>
+      <c r="F61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" s="20"/>
+      <c r="H61" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I61" s="18"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="18"/>
+      <c r="F62" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G62" s="20"/>
+      <c r="H62" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I62" s="18"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="18"/>
+      <c r="F63" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G63" s="20"/>
+      <c r="H63" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I63" s="18"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="18"/>
+      <c r="F64" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G64" s="20"/>
+      <c r="H64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I64" s="18"/>
+    </row>
+    <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="18"/>
+      <c r="F65" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G65" s="20"/>
+      <c r="H65" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I65" s="18"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="18"/>
+      <c r="F66" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G66" s="20"/>
+      <c r="H66" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I66" s="18"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="18"/>
+      <c r="F67" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G67" s="20"/>
+      <c r="H67" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I67" s="18"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="18"/>
+      <c r="F68" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G68" s="20"/>
+      <c r="H68" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I68" s="18"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="18"/>
+      <c r="F69" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G69" s="20"/>
+      <c r="H69" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I69" s="18"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="13"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" s="18"/>
+      <c r="F70" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G70" s="20"/>
+      <c r="H70" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I70" s="18"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="13"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="18"/>
+      <c r="F71" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G71" s="20"/>
+      <c r="H71" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I71" s="18"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="13"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="18"/>
+      <c r="F72" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G72" s="20"/>
+      <c r="H72" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I72" s="18"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="18"/>
+      <c r="F73" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G73" s="20"/>
+      <c r="H73" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I73" s="18"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="18"/>
+      <c r="F74" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G74" s="20"/>
+      <c r="H74" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I74" s="18"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" s="18"/>
+      <c r="F75" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G75" s="20"/>
+      <c r="H75" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I75" s="18"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="18"/>
+      <c r="F76" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G76" s="20"/>
+      <c r="H76" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I76" s="18"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="18"/>
+      <c r="F77" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I77" s="18"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="16"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="18"/>
+      <c r="F78" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G78" s="19"/>
+      <c r="H78" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I78" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="62">
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="I57:I77"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="G59:G76"/>
+    <mergeCell ref="E55:E78"/>
+    <mergeCell ref="A73:A78"/>
+    <mergeCell ref="B73:B78"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="A67:A72"/>
+    <mergeCell ref="B67:B72"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="B55:B60"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A31:Q31"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="A30:Q30"/>
+    <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="A29:Q29"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="A21:A26"/>
     <mergeCell ref="B9:B14"/>
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="A27:Q27"/>
@@ -2251,25 +2942,6 @@
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A31:Q31"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="B21:B26"/>
-    <mergeCell ref="A30:Q30"/>
-    <mergeCell ref="A28:Q28"/>
-    <mergeCell ref="A29:Q29"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/onlyMain/resources/节气数据.xlsx
+++ b/src/onlyMain/resources/节气数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Ecliptic\src\onlyMain\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\EclipticSeasons\src\onlyMain\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0B6EB0-1C42-412B-BF61-4C06EB398F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E1723B-E41A-4FE2-8B62-6CB84520CB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{9B4BF41A-40D4-4F30-95C5-B63DB59132D5}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="25580" windowHeight="13420" xr2:uid="{9B4BF41A-40D4-4F30-95C5-B63DB59132D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="143">
   <si>
     <t>立春</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -438,12 +438,179 @@
     <t>降雨基础概率为0.01/tick。对于无雨群系为0，几乎无雨群系为1%，少雨群系为10%，适量雨群系为40%，多雨群系为100%。最后乘群系概率（最少设计概率一半，除非无雨）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>热带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节气等价表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微凉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微暖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暖和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>略热</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏季平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏秋平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春夏平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不生长</t>
+  </si>
+  <si>
+    <t>不生长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>除夏季沿用立夏和小满平均外，其余早中晚沿用春夏秋的两个平均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冬+早春平均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生长概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础概率，依据标签和附加数据包确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隆冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>季春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>季夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浓秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渐春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>严冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冷地区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎热地区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温暖地区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +634,24 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -507,7 +692,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -530,13 +715,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -573,11 +787,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -586,6 +806,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -907,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349BBA73-A7C7-466C-AA4F-FD3A9580A8DC}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="7.5" style="1" customWidth="1"/>
@@ -924,27 +1165,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="20" t="s">
         <v>44</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
       <c r="J1" s="10" t="s">
         <v>49</v>
       </c>
@@ -957,20 +1198,20 @@
       <c r="M1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12" t="s">
+      <c r="O1" s="20"/>
+      <c r="P1" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="12"/>
+      <c r="Q1" s="20"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="10" t="s">
         <v>56</v>
       </c>
@@ -998,13 +1239,13 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="19" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1039,9 +1280,9 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1076,9 +1317,9 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1113,9 +1354,9 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1148,9 +1389,9 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1187,9 +1428,9 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1224,13 +1465,13 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1267,9 +1508,9 @@
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
@@ -1308,9 +1549,9 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1351,9 +1592,9 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1392,9 +1633,9 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1441,9 +1682,9 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1488,13 +1729,13 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -1539,9 +1780,9 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="6" t="s">
         <v>13</v>
       </c>
@@ -1584,9 +1825,9 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -1625,9 +1866,9 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="6" t="s">
         <v>15</v>
       </c>
@@ -1664,9 +1905,9 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15" t="s">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -1711,9 +1952,9 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
@@ -1756,13 +1997,13 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="16" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -1805,9 +2046,9 @@
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="8" t="s">
         <v>19</v>
       </c>
@@ -1848,9 +2089,9 @@
       <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -1885,9 +2126,9 @@
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
       <c r="D24" s="8" t="s">
         <v>21</v>
       </c>
@@ -1920,9 +2161,9 @@
       <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="8" t="s">
@@ -1957,9 +2198,9 @@
       <c r="Q25" s="8"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
       <c r="D26" s="8" t="s">
         <v>23</v>
       </c>
@@ -1992,127 +2233,127 @@
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
     </row>
     <row r="34" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G34" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="I34" s="12"/>
+      <c r="I34" s="20"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="I35" s="12"/>
+      <c r="I35" s="20"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="10" t="s">
@@ -2228,16 +2469,610 @@
       <c r="G46" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="12"/>
+      <c r="I46" s="20"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s">
+        <v>120</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" t="s">
+        <v>120</v>
+      </c>
+      <c r="H54" t="s">
+        <v>141</v>
+      </c>
+      <c r="I54" t="s">
+        <v>120</v>
+      </c>
+      <c r="J54" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="K54" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G55" t="s">
+        <v>116</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J55" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="K55" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="19"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G56" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I56" s="13"/>
+      <c r="J56" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="K56" s="23"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="19"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G57" s="15"/>
+      <c r="H57" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J57" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="K57" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="19"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G58" s="15"/>
+      <c r="H58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I58" s="13"/>
+      <c r="J58" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="K58" s="23"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="19"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I59" s="13"/>
+      <c r="J59" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K59" s="23"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="19"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G60" s="15"/>
+      <c r="H60" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I60" s="13"/>
+      <c r="J60" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K60" s="23"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G61" s="15"/>
+      <c r="H61" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I61" s="13"/>
+      <c r="J61" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K61" s="23"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="13"/>
+      <c r="F62" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G62" s="15"/>
+      <c r="H62" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I62" s="13"/>
+      <c r="J62" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K62" s="23"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G63" s="15"/>
+      <c r="H63" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I63" s="13"/>
+      <c r="J63" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K63" s="23"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G64" s="15"/>
+      <c r="H64" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I64" s="13"/>
+      <c r="J64" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K64" s="23"/>
+    </row>
+    <row r="65" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G65" s="15"/>
+      <c r="H65" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I65" s="13"/>
+      <c r="J65" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K65" s="23"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G66" s="15"/>
+      <c r="H66" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I66" s="13"/>
+      <c r="J66" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K66" s="23"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G67" s="15"/>
+      <c r="H67" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I67" s="13"/>
+      <c r="J67" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K67" s="23"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="13"/>
+      <c r="F68" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G68" s="15"/>
+      <c r="H68" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I68" s="13"/>
+      <c r="J68" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K68" s="23"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="13"/>
+      <c r="F69" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G69" s="15"/>
+      <c r="H69" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I69" s="13"/>
+      <c r="J69" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K69" s="23"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G70" s="15"/>
+      <c r="H70" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I70" s="13"/>
+      <c r="J70" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K70" s="23"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G71" s="15"/>
+      <c r="H71" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I71" s="13"/>
+      <c r="J71" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K71" s="23"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="13"/>
+      <c r="F72" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G72" s="15"/>
+      <c r="H72" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I72" s="13"/>
+      <c r="J72" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K72" s="23"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="13"/>
+      <c r="F73" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G73" s="15"/>
+      <c r="H73" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I73" s="13"/>
+      <c r="J73" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K73" s="23"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G74" s="15"/>
+      <c r="H74" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I74" s="13"/>
+      <c r="J74" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K74" s="23"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" s="13"/>
+      <c r="F75" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G75" s="15"/>
+      <c r="H75" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I75" s="13"/>
+      <c r="J75" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K75" s="23"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="13"/>
+      <c r="F76" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G76" s="15"/>
+      <c r="H76" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I76" s="13"/>
+      <c r="J76" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K76" s="23"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="13"/>
+      <c r="F77" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I77" s="13"/>
+      <c r="J77" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="K77" s="23"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="16"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="13"/>
+      <c r="F78" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G78" s="14"/>
+      <c r="H78" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I78" t="s">
+        <v>114</v>
+      </c>
+      <c r="J78" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="K78" s="21" t="s">
+        <v>114</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="A27:Q27"/>
+  <mergeCells count="64">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2249,9 +3084,6 @@
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A31:Q31"/>
@@ -2267,9 +3099,44 @@
     <mergeCell ref="A29:Q29"/>
     <mergeCell ref="A15:A20"/>
     <mergeCell ref="A21:A26"/>
+    <mergeCell ref="B9:B14"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="B55:B60"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="K57:K77"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="I57:I77"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="G59:G76"/>
+    <mergeCell ref="E55:E78"/>
+    <mergeCell ref="A73:A78"/>
+    <mergeCell ref="B73:B78"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="A67:A72"/>
+    <mergeCell ref="B67:B72"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C69:C70"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/onlyMain/resources/节气数据.xlsx
+++ b/src/onlyMain/resources/节气数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\EclipticSeasons\src\onlyMain\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98126537-EF22-4B50-87CE-B7B3FB5C5C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5B28AC-A903-4A7D-8D4C-AD1F877BADEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{9B4BF41A-40D4-4F30-95C5-B63DB59132D5}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="25580" windowHeight="13420" xr2:uid="{9B4BF41A-40D4-4F30-95C5-B63DB59132D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="143">
   <si>
     <t>立春</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -439,14 +439,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>温带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>热带</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -471,34 +463,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>极寒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>晚秋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中秋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>早秋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏季</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>早春</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中春</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>晚春</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -511,10 +483,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>寒冬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>晚冬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -551,6 +519,90 @@
   </si>
   <si>
     <t>基础概率，依据标签和附加数据包确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隆冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>季春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>季夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浓秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渐春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>严冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入冬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冷地区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎热地区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温暖地区</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -558,7 +610,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,6 +634,24 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -680,7 +750,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -717,19 +787,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -742,6 +809,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1080,27 +1165,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="24" t="s">
         <v>44</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
       <c r="J1" s="10" t="s">
         <v>49</v>
       </c>
@@ -1113,20 +1198,20 @@
       <c r="M1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14" t="s">
+      <c r="O1" s="24"/>
+      <c r="P1" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="14"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="10" t="s">
         <v>56</v>
       </c>
@@ -1154,13 +1239,13 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="23" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1195,9 +1280,9 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1232,9 +1317,9 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15" t="s">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1269,9 +1354,9 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1304,9 +1389,9 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1343,9 +1428,9 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1380,13 +1465,13 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="22" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1423,9 +1508,9 @@
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
@@ -1464,9 +1549,9 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1507,9 +1592,9 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1548,9 +1633,9 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1597,9 +1682,9 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1644,13 +1729,13 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -1695,9 +1780,9 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="6" t="s">
         <v>13</v>
       </c>
@@ -1740,9 +1825,9 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -1781,9 +1866,9 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="6" t="s">
         <v>15</v>
       </c>
@@ -1820,9 +1905,9 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -1867,9 +1952,9 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
@@ -1912,13 +1997,13 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="20" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -1961,9 +2046,9 @@
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="8" t="s">
         <v>19</v>
       </c>
@@ -2004,9 +2089,9 @@
       <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -2041,9 +2126,9 @@
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="8" t="s">
         <v>21</v>
       </c>
@@ -2076,9 +2161,9 @@
       <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="8" t="s">
@@ -2113,9 +2198,9 @@
       <c r="Q25" s="8"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="8" t="s">
         <v>23</v>
       </c>
@@ -2148,127 +2233,127 @@
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
     </row>
     <row r="34" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G34" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H34" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="I34" s="14"/>
+      <c r="I34" s="24"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="H35" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="I35" s="14"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="10" t="s">
@@ -2384,502 +2469,658 @@
       <c r="G46" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H46" s="14" t="s">
+      <c r="H46" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="14"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
+      <c r="I46" s="24"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
       <c r="D54" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s">
+        <v>120</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" t="s">
+        <v>120</v>
+      </c>
+      <c r="H54" t="s">
+        <v>141</v>
+      </c>
+      <c r="I54" t="s">
+        <v>120</v>
+      </c>
+      <c r="J54" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E54" t="s">
-        <v>128</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G54" t="s">
-        <v>128</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="K54" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G55" t="s">
+        <v>116</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I55" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="J55" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="I54" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G55" t="s">
-        <v>124</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I55" s="18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
+      <c r="K55" s="25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
       <c r="D56" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E56" s="18"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>127</v>
+        <v>112</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>119</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I56" s="18"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I56" s="17"/>
+      <c r="J56" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="K56" s="25"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E57" s="18"/>
+      <c r="E57" s="17"/>
       <c r="F57" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G57" s="20"/>
-      <c r="H57" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I57" s="18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
+        <v>112</v>
+      </c>
+      <c r="G57" s="19"/>
+      <c r="H57" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I57" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K57" s="25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
       <c r="D58" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="18"/>
+      <c r="E58" s="17"/>
       <c r="F58" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G58" s="20"/>
-      <c r="H58" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I58" s="18"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G58" s="19"/>
+      <c r="H58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I58" s="17"/>
+      <c r="J58" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K58" s="25"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23" t="s">
         <v>26</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="18"/>
+      <c r="E59" s="17"/>
       <c r="F59" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G59" s="20" t="s">
-        <v>126</v>
+        <v>108</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>118</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I59" s="18"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
+        <v>130</v>
+      </c>
+      <c r="I59" s="17"/>
+      <c r="J59" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K59" s="25"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="23"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
       <c r="D60" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="18"/>
+      <c r="E60" s="17"/>
       <c r="F60" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G60" s="20"/>
+        <v>108</v>
+      </c>
+      <c r="G60" s="19"/>
       <c r="H60" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I60" s="18"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I60" s="17"/>
+      <c r="J60" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K60" s="25"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="22" t="s">
         <v>27</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E61" s="18"/>
+      <c r="E61" s="17"/>
       <c r="F61" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G61" s="20"/>
+        <v>134</v>
+      </c>
+      <c r="G61" s="19"/>
       <c r="H61" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I61" s="18"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
+        <v>126</v>
+      </c>
+      <c r="I61" s="17"/>
+      <c r="J61" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K61" s="25"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
       <c r="D62" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="18"/>
+      <c r="E62" s="17"/>
       <c r="F62" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G62" s="20"/>
+        <v>109</v>
+      </c>
+      <c r="G62" s="19"/>
       <c r="H62" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I62" s="18"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I62" s="17"/>
+      <c r="J62" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K62" s="25"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22" t="s">
         <v>28</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E63" s="18"/>
+      <c r="E63" s="17"/>
       <c r="F63" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G63" s="20"/>
+        <v>130</v>
+      </c>
+      <c r="G63" s="19"/>
       <c r="H63" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I63" s="18"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
+        <v>131</v>
+      </c>
+      <c r="I63" s="17"/>
+      <c r="J63" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K63" s="25"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="22"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
       <c r="D64" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="18"/>
+      <c r="E64" s="17"/>
       <c r="F64" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G64" s="20"/>
+        <v>139</v>
+      </c>
+      <c r="G64" s="19"/>
       <c r="H64" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I64" s="18"/>
-    </row>
-    <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="I64" s="17"/>
+      <c r="J64" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K64" s="25"/>
+    </row>
+    <row r="65" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22" t="s">
         <v>29</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="18"/>
+      <c r="E65" s="17"/>
       <c r="F65" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G65" s="20"/>
+        <v>128</v>
+      </c>
+      <c r="G65" s="19"/>
       <c r="H65" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I65" s="18"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
+        <v>127</v>
+      </c>
+      <c r="I65" s="17"/>
+      <c r="J65" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K65" s="25"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="22"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
       <c r="D66" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E66" s="18"/>
+      <c r="E66" s="17"/>
       <c r="F66" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G66" s="20"/>
+        <v>133</v>
+      </c>
+      <c r="G66" s="19"/>
       <c r="H66" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I66" s="18"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I66" s="17"/>
+      <c r="J66" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K66" s="25"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E67" s="18"/>
+      <c r="E67" s="17"/>
       <c r="F67" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G67" s="20"/>
+        <v>132</v>
+      </c>
+      <c r="G67" s="19"/>
       <c r="H67" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I67" s="18"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
+        <v>127</v>
+      </c>
+      <c r="I67" s="17"/>
+      <c r="J67" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K67" s="25"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="21"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
       <c r="D68" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E68" s="18"/>
+      <c r="E68" s="17"/>
       <c r="F68" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G68" s="20"/>
+        <v>107</v>
+      </c>
+      <c r="G68" s="19"/>
       <c r="H68" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I68" s="18"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I68" s="17"/>
+      <c r="J68" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K68" s="25"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="21"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21" t="s">
         <v>31</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E69" s="18"/>
+      <c r="E69" s="17"/>
       <c r="F69" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G69" s="20"/>
+        <v>137</v>
+      </c>
+      <c r="G69" s="19"/>
       <c r="H69" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I69" s="18"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
+        <v>129</v>
+      </c>
+      <c r="I69" s="17"/>
+      <c r="J69" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K69" s="25"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="21"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
       <c r="D70" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="18"/>
+      <c r="E70" s="17"/>
       <c r="F70" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G70" s="20"/>
+        <v>110</v>
+      </c>
+      <c r="G70" s="19"/>
       <c r="H70" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I70" s="18"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I70" s="17"/>
+      <c r="J70" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K70" s="25"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="21"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E71" s="18"/>
+      <c r="E71" s="17"/>
       <c r="F71" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G71" s="20"/>
+        <v>111</v>
+      </c>
+      <c r="G71" s="19"/>
       <c r="H71" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I71" s="18"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
+        <v>128</v>
+      </c>
+      <c r="I71" s="17"/>
+      <c r="J71" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K71" s="25"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="21"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21"/>
       <c r="D72" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E72" s="18"/>
+      <c r="E72" s="17"/>
       <c r="F72" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G72" s="20"/>
+        <v>111</v>
+      </c>
+      <c r="G72" s="19"/>
       <c r="H72" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I72" s="18"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="I72" s="17"/>
+      <c r="J72" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K72" s="25"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="20" t="s">
         <v>33</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E73" s="18"/>
+      <c r="E73" s="17"/>
       <c r="F73" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G73" s="20"/>
-      <c r="H73" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I73" s="18"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="16"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
+        <v>111</v>
+      </c>
+      <c r="G73" s="19"/>
+      <c r="H73" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I73" s="17"/>
+      <c r="J73" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K73" s="25"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="20"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E74" s="18"/>
+      <c r="E74" s="17"/>
       <c r="F74" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G74" s="20"/>
-      <c r="H74" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I74" s="18"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="16"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G74" s="19"/>
+      <c r="H74" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I74" s="17"/>
+      <c r="J74" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K74" s="25"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="20"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E75" s="18"/>
+      <c r="E75" s="17"/>
       <c r="F75" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G75" s="20"/>
-      <c r="H75" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G75" s="19"/>
+      <c r="H75" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I75" s="18"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="16"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K75" s="25"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="20"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E76" s="18"/>
+      <c r="E76" s="17"/>
       <c r="F76" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G76" s="20"/>
-      <c r="H76" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I76" s="18"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="16"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G76" s="19"/>
+      <c r="H76" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I76" s="17"/>
+      <c r="J76" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K76" s="25"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="20"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20" t="s">
         <v>35</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E77" s="18"/>
+      <c r="E77" s="17"/>
       <c r="F77" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I77" s="18"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="16"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
+        <v>135</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I77" s="17"/>
+      <c r="J77" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K77" s="25"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="20"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
       <c r="D78" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E78" s="18"/>
+      <c r="E78" s="17"/>
       <c r="F78" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G78" s="19"/>
-      <c r="H78" s="6" t="s">
-        <v>105</v>
+        <v>135</v>
+      </c>
+      <c r="G78" s="18"/>
+      <c r="H78" s="8" t="s">
+        <v>124</v>
       </c>
       <c r="I78" t="s">
-        <v>122</v>
+        <v>114</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="64">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A31:Q31"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="A30:Q30"/>
+    <mergeCell ref="A28:Q28"/>
+    <mergeCell ref="A29:Q29"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="B55:B60"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="K57:K77"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C65:C66"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="I57:I77"/>
     <mergeCell ref="I55:I56"/>
@@ -2896,52 +3137,6 @@
     <mergeCell ref="B67:B72"/>
     <mergeCell ref="C67:C68"/>
     <mergeCell ref="C69:C70"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="A61:A66"/>
-    <mergeCell ref="B61:B66"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="A55:A60"/>
-    <mergeCell ref="B55:B60"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A31:Q31"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="B21:B26"/>
-    <mergeCell ref="A30:Q30"/>
-    <mergeCell ref="A28:Q28"/>
-    <mergeCell ref="A29:Q29"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="A27:Q27"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C23:C24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
